--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121569646</v>
       </c>
       <c r="B2" t="n">
-        <v>91159</v>
+        <v>91160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121569647</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569657</v>
+        <v>121569650</v>
       </c>
       <c r="B4" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646535</v>
+        <v>646237</v>
       </c>
       <c r="R4" t="n">
-        <v>7168682</v>
+        <v>7168507</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569655</v>
+        <v>121569656</v>
       </c>
       <c r="B5" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646531</v>
+        <v>646512</v>
       </c>
       <c r="R5" t="n">
-        <v>7168646</v>
+        <v>7168641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
         <v>121569644</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569656</v>
+        <v>121569655</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646512</v>
+        <v>646531</v>
       </c>
       <c r="R7" t="n">
-        <v>7168641</v>
+        <v>7168646</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569652</v>
+        <v>121569649</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>98022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646381</v>
+        <v>646197</v>
       </c>
       <c r="R8" t="n">
-        <v>7168550</v>
+        <v>7168431</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569653</v>
+        <v>121569657</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646391</v>
+        <v>646535</v>
       </c>
       <c r="R9" t="n">
-        <v>7168546</v>
+        <v>7168682</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569649</v>
+        <v>121569652</v>
       </c>
       <c r="B10" t="n">
-        <v>98021</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646197</v>
+        <v>646381</v>
       </c>
       <c r="R10" t="n">
-        <v>7168431</v>
+        <v>7168550</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569651</v>
+        <v>121569653</v>
       </c>
       <c r="B11" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646323</v>
+        <v>646391</v>
       </c>
       <c r="R11" t="n">
-        <v>7168558</v>
+        <v>7168546</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569650</v>
+        <v>121569651</v>
       </c>
       <c r="B12" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646237</v>
+        <v>646323</v>
       </c>
       <c r="R12" t="n">
-        <v>7168507</v>
+        <v>7168558</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569650</v>
+        <v>121569644</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646237</v>
+        <v>646269</v>
       </c>
       <c r="R4" t="n">
-        <v>7168507</v>
+        <v>7168612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569656</v>
+        <v>121569650</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646512</v>
+        <v>646237</v>
       </c>
       <c r="R5" t="n">
-        <v>7168641</v>
+        <v>7168507</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569644</v>
+        <v>121569655</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646269</v>
+        <v>646531</v>
       </c>
       <c r="R6" t="n">
-        <v>7168612</v>
+        <v>7168646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569655</v>
+        <v>121569652</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646531</v>
+        <v>646381</v>
       </c>
       <c r="R7" t="n">
-        <v>7168646</v>
+        <v>7168550</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569649</v>
+        <v>121569651</v>
       </c>
       <c r="B8" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646197</v>
+        <v>646323</v>
       </c>
       <c r="R8" t="n">
-        <v>7168431</v>
+        <v>7168558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569652</v>
+        <v>121569653</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646381</v>
+        <v>646391</v>
       </c>
       <c r="R10" t="n">
-        <v>7168550</v>
+        <v>7168546</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569653</v>
+        <v>121569656</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646391</v>
+        <v>646512</v>
       </c>
       <c r="R11" t="n">
-        <v>7168546</v>
+        <v>7168641</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569651</v>
+        <v>121569649</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646323</v>
+        <v>646197</v>
       </c>
       <c r="R12" t="n">
-        <v>7168558</v>
+        <v>7168431</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569646</v>
+        <v>121569647</v>
       </c>
       <c r="B2" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646132</v>
+        <v>646125</v>
       </c>
       <c r="R2" t="n">
-        <v>7168437</v>
+        <v>7168422</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569647</v>
+        <v>121569646</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646125</v>
+        <v>646132</v>
       </c>
       <c r="R3" t="n">
-        <v>7168422</v>
+        <v>7168437</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569644</v>
+        <v>121569650</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646269</v>
+        <v>646237</v>
       </c>
       <c r="R4" t="n">
-        <v>7168612</v>
+        <v>7168507</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569650</v>
+        <v>121569657</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646237</v>
+        <v>646535</v>
       </c>
       <c r="R5" t="n">
-        <v>7168507</v>
+        <v>7168682</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569655</v>
+        <v>121569652</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646531</v>
+        <v>646381</v>
       </c>
       <c r="R6" t="n">
-        <v>7168646</v>
+        <v>7168550</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569652</v>
+        <v>121569651</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646381</v>
+        <v>646323</v>
       </c>
       <c r="R7" t="n">
-        <v>7168550</v>
+        <v>7168558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569651</v>
+        <v>121569644</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646323</v>
+        <v>646269</v>
       </c>
       <c r="R8" t="n">
-        <v>7168558</v>
+        <v>7168612</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569657</v>
+        <v>121569656</v>
       </c>
       <c r="B9" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646535</v>
+        <v>646512</v>
       </c>
       <c r="R9" t="n">
-        <v>7168682</v>
+        <v>7168641</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569656</v>
+        <v>121569649</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>98022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646512</v>
+        <v>646197</v>
       </c>
       <c r="R11" t="n">
-        <v>7168641</v>
+        <v>7168431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569649</v>
+        <v>121569655</v>
       </c>
       <c r="B12" t="n">
-        <v>98022</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646197</v>
+        <v>646531</v>
       </c>
       <c r="R12" t="n">
-        <v>7168431</v>
+        <v>7168646</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569650</v>
+        <v>121569649</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646237</v>
+        <v>646197</v>
       </c>
       <c r="R4" t="n">
-        <v>7168507</v>
+        <v>7168431</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569657</v>
+        <v>121569656</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646535</v>
+        <v>646512</v>
       </c>
       <c r="R5" t="n">
-        <v>7168682</v>
+        <v>7168641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569652</v>
+        <v>121569650</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646381</v>
+        <v>646237</v>
       </c>
       <c r="R6" t="n">
-        <v>7168550</v>
+        <v>7168507</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569651</v>
+        <v>121569652</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646323</v>
+        <v>646381</v>
       </c>
       <c r="R7" t="n">
-        <v>7168558</v>
+        <v>7168550</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569644</v>
+        <v>121569657</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646269</v>
+        <v>646535</v>
       </c>
       <c r="R8" t="n">
-        <v>7168612</v>
+        <v>7168682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569656</v>
+        <v>121569655</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646512</v>
+        <v>646531</v>
       </c>
       <c r="R9" t="n">
-        <v>7168641</v>
+        <v>7168646</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569653</v>
+        <v>121569644</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646391</v>
+        <v>646269</v>
       </c>
       <c r="R10" t="n">
-        <v>7168546</v>
+        <v>7168612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569649</v>
+        <v>121569651</v>
       </c>
       <c r="B11" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646197</v>
+        <v>646323</v>
       </c>
       <c r="R11" t="n">
-        <v>7168431</v>
+        <v>7168558</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569655</v>
+        <v>121569653</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646531</v>
+        <v>646391</v>
       </c>
       <c r="R12" t="n">
-        <v>7168646</v>
+        <v>7168546</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569656</v>
+        <v>121569650</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646512</v>
+        <v>646237</v>
       </c>
       <c r="R5" t="n">
-        <v>7168641</v>
+        <v>7168507</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569650</v>
+        <v>121569656</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646237</v>
+        <v>646512</v>
       </c>
       <c r="R6" t="n">
-        <v>7168507</v>
+        <v>7168641</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121569647</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121569646</v>
       </c>
       <c r="B3" t="n">
-        <v>91160</v>
+        <v>91168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569649</v>
+        <v>121569651</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646197</v>
+        <v>646323</v>
       </c>
       <c r="R4" t="n">
-        <v>7168431</v>
+        <v>7168558</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569650</v>
+        <v>121569655</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646237</v>
+        <v>646531</v>
       </c>
       <c r="R5" t="n">
-        <v>7168507</v>
+        <v>7168646</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569656</v>
+        <v>121569657</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646512</v>
+        <v>646535</v>
       </c>
       <c r="R6" t="n">
-        <v>7168641</v>
+        <v>7168682</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569652</v>
+        <v>121569656</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646381</v>
+        <v>646512</v>
       </c>
       <c r="R7" t="n">
-        <v>7168550</v>
+        <v>7168641</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569657</v>
+        <v>121569652</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646535</v>
+        <v>646381</v>
       </c>
       <c r="R8" t="n">
-        <v>7168682</v>
+        <v>7168550</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569655</v>
+        <v>121569644</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646531</v>
+        <v>646269</v>
       </c>
       <c r="R9" t="n">
-        <v>7168646</v>
+        <v>7168612</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569644</v>
+        <v>121569650</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646269</v>
+        <v>646237</v>
       </c>
       <c r="R10" t="n">
-        <v>7168612</v>
+        <v>7168507</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569651</v>
+        <v>121569649</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>98030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646323</v>
+        <v>646197</v>
       </c>
       <c r="R11" t="n">
-        <v>7168558</v>
+        <v>7168431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1698,7 +1698,7 @@
         <v>121569653</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569656</v>
+        <v>121569652</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646512</v>
+        <v>646381</v>
       </c>
       <c r="R7" t="n">
-        <v>7168641</v>
+        <v>7168550</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569652</v>
+        <v>121569644</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646381</v>
+        <v>646269</v>
       </c>
       <c r="R8" t="n">
-        <v>7168550</v>
+        <v>7168612</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569644</v>
+        <v>121569656</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646269</v>
+        <v>646512</v>
       </c>
       <c r="R9" t="n">
-        <v>7168612</v>
+        <v>7168641</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569647</v>
+        <v>121569646</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646125</v>
+        <v>646132</v>
       </c>
       <c r="R2" t="n">
-        <v>7168422</v>
+        <v>7168437</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569646</v>
+        <v>121569647</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646132</v>
+        <v>646125</v>
       </c>
       <c r="R3" t="n">
-        <v>7168437</v>
+        <v>7168422</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569656</v>
+        <v>121569650</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646512</v>
+        <v>646237</v>
       </c>
       <c r="R4" t="n">
-        <v>7168641</v>
+        <v>7168507</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569655</v>
+        <v>121569656</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646531</v>
+        <v>646512</v>
       </c>
       <c r="R5" t="n">
-        <v>7168646</v>
+        <v>7168641</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569653</v>
+        <v>121569652</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646391</v>
+        <v>646381</v>
       </c>
       <c r="R6" t="n">
-        <v>7168546</v>
+        <v>7168550</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569657</v>
+        <v>121569644</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646535</v>
+        <v>646269</v>
       </c>
       <c r="R7" t="n">
-        <v>7168682</v>
+        <v>7168612</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569652</v>
+        <v>121569657</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646381</v>
+        <v>646535</v>
       </c>
       <c r="R8" t="n">
-        <v>7168550</v>
+        <v>7168682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569644</v>
+        <v>121569655</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646269</v>
+        <v>646531</v>
       </c>
       <c r="R9" t="n">
-        <v>7168612</v>
+        <v>7168646</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569650</v>
+        <v>121569653</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646237</v>
+        <v>646391</v>
       </c>
       <c r="R12" t="n">
-        <v>7168507</v>
+        <v>7168546</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569650</v>
+        <v>121569655</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646237</v>
+        <v>646531</v>
       </c>
       <c r="R4" t="n">
-        <v>7168507</v>
+        <v>7168646</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569656</v>
+        <v>121569652</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646512</v>
+        <v>646381</v>
       </c>
       <c r="R5" t="n">
-        <v>7168641</v>
+        <v>7168550</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569652</v>
+        <v>121569649</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>98030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646381</v>
+        <v>646197</v>
       </c>
       <c r="R6" t="n">
-        <v>7168550</v>
+        <v>7168431</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569644</v>
+        <v>121569657</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646269</v>
+        <v>646535</v>
       </c>
       <c r="R7" t="n">
-        <v>7168612</v>
+        <v>7168682</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569657</v>
+        <v>121569651</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646535</v>
+        <v>646323</v>
       </c>
       <c r="R8" t="n">
-        <v>7168682</v>
+        <v>7168558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569655</v>
+        <v>121569656</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646531</v>
+        <v>646512</v>
       </c>
       <c r="R9" t="n">
-        <v>7168646</v>
+        <v>7168641</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569651</v>
+        <v>121569644</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646323</v>
+        <v>646269</v>
       </c>
       <c r="R10" t="n">
-        <v>7168558</v>
+        <v>7168612</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569649</v>
+        <v>121569650</v>
       </c>
       <c r="B11" t="n">
-        <v>98030</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646197</v>
+        <v>646237</v>
       </c>
       <c r="R11" t="n">
-        <v>7168431</v>
+        <v>7168507</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121569647</v>
       </c>
       <c r="B2" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,16 +775,11 @@
         <v>121569646</v>
       </c>
       <c r="B3" t="n">
-        <v>91182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -802,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569657</v>
+        <v>121569644</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646535</v>
+        <v>646269</v>
       </c>
       <c r="R4" t="n">
-        <v>7168682</v>
+        <v>7168612</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569655</v>
+        <v>121569652</v>
       </c>
       <c r="B5" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646531</v>
+        <v>646381</v>
       </c>
       <c r="R5" t="n">
-        <v>7168646</v>
+        <v>7168550</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569652</v>
+        <v>121569653</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646381</v>
+        <v>646391</v>
       </c>
       <c r="R6" t="n">
-        <v>7168550</v>
+        <v>7168546</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569644</v>
+        <v>121569650</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646269</v>
+        <v>646237</v>
       </c>
       <c r="R7" t="n">
-        <v>7168612</v>
+        <v>7168507</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,16 +1260,11 @@
         <v>121569651</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569649</v>
+        <v>121569656</v>
       </c>
       <c r="B9" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646197</v>
+        <v>646512</v>
       </c>
       <c r="R9" t="n">
-        <v>7168431</v>
+        <v>7168641</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569653</v>
+        <v>121569657</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646391</v>
+        <v>646535</v>
       </c>
       <c r="R10" t="n">
-        <v>7168546</v>
+        <v>7168682</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569656</v>
+        <v>121569649</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646512</v>
+        <v>646197</v>
       </c>
       <c r="R11" t="n">
-        <v>7168641</v>
+        <v>7168431</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1692,108 +1642,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>121569650</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Fäboliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>646237</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7168507</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9327-2022 artfynd.xlsx
+++ b/artfynd/A 9327-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569647</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569644</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569653</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569650</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569651</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569656</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569657</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>